--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -148,6 +148,267 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco bilmiyorum</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco bilmiyorum</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco bilmiyorum</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -192,6 +453,37 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -313,12 +605,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -341,10 +633,10 @@
         <v>81</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -166,7 +166,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtr71fv1-0</t>
+          <t xml:space="preserve">v-mtr71fv1-1</t>
         </is>
       </c>
     </row>
@@ -253,7 +253,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -318,31 +318,11 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtr71fv1-1</t>
+          <t xml:space="preserve">v-mtr71fv1-2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAro box deneme</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A3</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK g1 KO</t>
@@ -400,12 +380,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtr71fv1-2</t>
+          <t xml:space="preserve">v-mtr71fv1-0</t>
         </is>
       </c>
     </row>
@@ -475,10 +455,10 @@
         </is>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -543,6 +523,53 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -633,10 +660,10 @@
         <v>81</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -149,21 +149,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAro box deneme</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">A2</t>
@@ -236,21 +221,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAro box deneme</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">A3</t>
@@ -534,21 +504,6 @@
           <t xml:space="preserve">HEK g1 KO</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAro box deneme</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">A1</t>
@@ -632,17 +587,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack 1</t>
+          <t xml:space="preserve">Not placed yet</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAro box deneme</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -660,10 +615,10 @@
         <v>81</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -149,11 +149,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A2</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK g1 KO</t>
@@ -211,84 +206,79 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t xml:space="preserve">v-mtr71fv1-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco bilmiyorum</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t xml:space="preserve">v-mtr71fv1-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A3</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK g1 KO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">myco bilmiyorum</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-mtr71fv1-2</t>
         </is>
       </c>
     </row>
@@ -355,7 +345,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtr71fv1-0</t>
+          <t xml:space="preserve">v-mtr71fv1-2</t>
         </is>
       </c>
     </row>
@@ -425,13 +415,13 @@
         </is>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -525,6 +515,80 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">discarded</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme was removed from the freezer; this withdrawal was missed at the time</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK g1 KO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repair</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">discarded</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme was removed from the freezer; this withdrawal was missed at the time</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtr71fv1-2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -621,6 +685,228 @@
         <v>81</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>81</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>81</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DUZENLE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>81</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ONGOING</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>81</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unnamed box</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>81</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -651,17 +651,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -688,17 +688,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -725,17 +725,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -762,17 +762,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -799,17 +799,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -836,17 +836,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">Unnamed box</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -870,43 +870,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grid</t>
-        </is>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>81</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>81</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -184,14 +184,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -261,14 +261,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -338,14 +338,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -415,14 +415,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1262,14 +1262,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1339,14 +1339,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-02-10</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">10.02.20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1570,14 +1570,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1647,14 +1647,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1724,14 +1724,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1801,14 +1801,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1878,14 +1878,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-01-01</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">01.01.20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2678,14 +2678,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">04.09.20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2755,14 +2755,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">04.09.20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2832,14 +2832,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-04</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">04.09.20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2909,14 +2909,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-06</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2986,14 +2986,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-06</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">06.08.20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3063,14 +3063,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3145,14 +3145,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3227,14 +3227,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3309,14 +3309,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3391,14 +3391,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3473,14 +3473,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-08-01</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">01.08.20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4094,14 +4094,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">08.07.20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4171,14 +4171,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">08.07.20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4248,14 +4248,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">08.07.20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4325,14 +4325,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-08</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">08.07.20</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5125,14 +5125,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">10.07.20</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5202,14 +5202,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">10.07.20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5279,14 +5279,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">10.07.20</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5818,14 +5818,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">10.07.20</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5895,14 +5895,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-07-10</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">10.07.20</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5972,14 +5972,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6054,14 +6054,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6136,14 +6136,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6218,14 +6218,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6300,14 +6300,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6382,14 +6382,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-03-02</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">02.03.20</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7100,14 +7100,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-11</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">11.06.21</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7592,14 +7592,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-07</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">07.06.21</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -7674,14 +7674,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-07</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">07.06.21</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -7756,14 +7756,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-07</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">07.06.21</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7838,14 +7838,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-07</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">07.06.21</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7920,14 +7920,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021-06-07</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">07.06.21</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -37727,14 +37727,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-10-12</t>
+        </is>
+      </c>
       <c r="I506" t="inlineStr">
         <is>
           <t xml:space="preserve">12.10.23</t>
-        </is>
-      </c>
-      <c r="J506" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
@@ -37809,14 +37809,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-10-12</t>
+        </is>
+      </c>
       <c r="I507" t="inlineStr">
         <is>
           <t xml:space="preserve">12.10.23</t>
-        </is>
-      </c>
-      <c r="J507" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
@@ -37891,14 +37891,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-10-12</t>
+        </is>
+      </c>
       <c r="I508" t="inlineStr">
         <is>
           <t xml:space="preserve">12.10.23</t>
-        </is>
-      </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
@@ -38055,14 +38055,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I510" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
@@ -38137,14 +38137,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I511" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
@@ -38219,14 +38219,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I512" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J512" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
@@ -38301,14 +38301,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I513" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J513" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
@@ -38383,14 +38383,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I514" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J514" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -38465,14 +38465,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I515" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J515" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -38547,14 +38547,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-11-02</t>
+        </is>
+      </c>
       <c r="I516" t="inlineStr">
         <is>
           <t xml:space="preserve">02.11.23</t>
-        </is>
-      </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -3719,6 +3719,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -3796,6 +3801,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -6551,6 +6561,11 @@
           <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -31848,6 +31863,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -32119,6 +32139,11 @@
       <c r="J428" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -3883,6 +3883,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -3960,6 +3965,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -6484,6 +6494,11 @@
           <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -30721,6 +30736,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -31935,6 +31955,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -32074,6 +32099,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -32561,6 +32591,11 @@
       <c r="J434" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -194,6 +194,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -271,6 +276,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -348,6 +358,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -425,6 +440,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -502,6 +522,11 @@
           <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -579,6 +604,11 @@
           <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -656,6 +686,11 @@
           <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -733,6 +768,11 @@
           <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -810,6 +850,11 @@
           <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -887,6 +932,11 @@
           <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -964,6 +1014,11 @@
           <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1041,6 +1096,11 @@
           <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1118,6 +1178,11 @@
           <t xml:space="preserve">14.12.19</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1195,6 +1260,11 @@
           <t xml:space="preserve">15.12.19</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1272,6 +1342,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1349,6 +1424,11 @@
           <t xml:space="preserve">10.02.20</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1426,6 +1506,11 @@
           <t xml:space="preserve">22.12.19</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1503,6 +1588,11 @@
           <t xml:space="preserve">22.12.19</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1580,6 +1670,11 @@
           <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1657,6 +1752,11 @@
           <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1734,6 +1834,11 @@
           <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1811,6 +1916,11 @@
           <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -1888,6 +1998,11 @@
           <t xml:space="preserve">01.01.20</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2919,6 +3034,11 @@
           <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -2996,6 +3116,11 @@
           <t xml:space="preserve">06.08.20</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -4047,6 +4172,11 @@
           <t xml:space="preserve">16.07.20</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -5386,6 +5516,11 @@
           <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -5463,6 +5598,11 @@
           <t xml:space="preserve">17.02.20</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -7063,6 +7203,11 @@
           <t xml:space="preserve">29.03.21</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -15674,7 +15819,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -16732,7 +16877,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -17266,7 +17411,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -17343,7 +17488,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -18416,7 +18561,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -18493,7 +18638,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -18570,7 +18715,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -18647,7 +18792,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -18801,7 +18946,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -18955,7 +19100,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -19032,7 +19177,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -19725,7 +19870,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -20033,7 +20178,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -20182,7 +20327,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21406,7 +21551,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -21550,7 +21695,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -21622,7 +21767,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -21766,7 +21911,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -21910,7 +22055,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -21982,7 +22127,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -22769,7 +22914,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -22913,7 +23058,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24554,7 +24699,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -24626,7 +24771,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -25341,7 +25486,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -26334,7 +26479,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -27178,7 +27323,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -27250,7 +27395,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -28099,7 +28244,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -37583,7 +37728,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R503" t="inlineStr">
@@ -37983,7 +38128,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R508" t="inlineStr">
@@ -38065,7 +38210,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R509" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -30677,7 +30677,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -30749,7 +30749,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -31469,7 +31469,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -31896,7 +31896,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -32894,7 +32894,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -36196,7 +36196,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -36268,7 +36268,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -36340,7 +36340,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -36412,7 +36412,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -36556,7 +36556,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -36700,7 +36700,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -36772,7 +36772,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -36916,7 +36916,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -37132,7 +37132,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -37204,7 +37204,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -37276,7 +37276,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -37420,7 +37420,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -37492,7 +37492,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CabaR</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -57317,6 +57317,117 @@
         <v>6</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>81</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>81</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -56997,7 +56997,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -199,11 +199,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -281,11 +276,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -363,11 +353,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -445,11 +430,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -527,11 +507,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -609,11 +584,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -691,11 +661,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -773,11 +738,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -855,11 +815,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -937,11 +892,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1019,11 +969,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1101,11 +1046,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1183,11 +1123,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1265,11 +1200,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1347,11 +1277,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1429,11 +1354,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1511,11 +1431,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1593,11 +1508,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1675,11 +1585,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1757,11 +1662,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1839,11 +1739,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1921,11 +1816,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2003,11 +1893,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2080,11 +1965,6 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2157,11 +2037,6 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2234,11 +2109,6 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2316,11 +2186,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2398,11 +2263,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2480,11 +2340,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2562,11 +2417,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2644,11 +2494,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2726,11 +2571,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2803,11 +2643,6 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2880,11 +2715,6 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2957,11 +2787,6 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3039,11 +2864,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3121,11 +2941,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3203,11 +3018,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3285,11 +3095,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3367,11 +3172,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3449,11 +3249,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3531,11 +3326,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3613,11 +3403,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3690,11 +3475,6 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3767,11 +3547,6 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3849,11 +3624,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3931,11 +3701,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4013,11 +3778,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4095,11 +3855,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4177,11 +3932,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4254,11 +4004,6 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4331,11 +4076,6 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4408,11 +4148,6 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4485,11 +4220,6 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4562,11 +4292,6 @@
           <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4644,11 +4369,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4726,11 +4446,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4808,11 +4523,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4890,11 +4600,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4972,11 +4677,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5054,11 +4754,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5131,11 +4826,6 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5208,11 +4898,6 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5285,11 +4970,6 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5362,11 +5042,6 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5439,11 +5114,6 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5521,11 +5191,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5603,11 +5268,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5680,11 +5340,6 @@
           <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -5757,11 +5412,6 @@
           <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -5834,11 +5484,6 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5911,11 +5556,6 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5988,11 +5628,6 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6065,11 +5700,6 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6147,11 +5777,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6229,11 +5854,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6311,11 +5931,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6393,11 +6008,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6475,11 +6085,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6557,11 +6162,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6639,11 +6239,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6721,11 +6316,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6798,11 +6388,6 @@
           <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -6880,11 +6465,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6962,11 +6542,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -7044,11 +6619,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -7126,11 +6696,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7208,11 +6773,6 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7290,11 +6850,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7372,11 +6927,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7454,11 +7004,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7536,11 +7081,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7618,11 +7158,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7700,11 +7235,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7782,11 +7312,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7864,11 +7389,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7946,11 +7466,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8028,11 +7543,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8110,11 +7620,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8192,11 +7697,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8274,11 +7774,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8351,11 +7846,6 @@
           <t xml:space="preserve">26.12.19</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8428,11 +7918,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -8500,11 +7985,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8577,11 +8057,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -8654,11 +8129,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -8731,11 +8201,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -8808,11 +8273,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8885,11 +8345,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8962,11 +8417,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9039,11 +8489,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9116,11 +8561,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -9193,11 +8633,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9270,11 +8705,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9347,11 +8777,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9424,11 +8849,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9501,11 +8921,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9578,11 +8993,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9655,11 +9065,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9732,11 +9137,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9809,11 +9209,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9886,11 +9281,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9963,11 +9353,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10040,11 +9425,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10117,11 +9497,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10194,11 +9569,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10271,11 +9641,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10348,11 +9713,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10425,11 +9785,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10502,11 +9857,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10579,11 +9929,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10656,11 +10001,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10733,11 +10073,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10810,11 +10145,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10887,11 +10217,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10959,11 +10284,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11031,11 +10351,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11108,11 +10423,6 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11185,11 +10495,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11262,11 +10567,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11339,11 +10639,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11416,11 +10711,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -11493,11 +10783,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11570,11 +10855,6 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11647,11 +10927,6 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11724,11 +10999,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11801,11 +11071,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11878,11 +11143,6 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11950,11 +11210,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12027,11 +11282,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12099,11 +11349,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12171,11 +11416,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12248,11 +11488,6 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12325,11 +11560,6 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12397,11 +11627,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12474,11 +11699,6 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12546,11 +11766,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12623,11 +11838,6 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12695,11 +11905,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12772,11 +11977,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12849,11 +12049,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12926,11 +12121,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -13003,11 +12193,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13080,11 +12265,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13157,11 +12337,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13234,11 +12409,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13311,11 +12481,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13388,11 +12553,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13465,11 +12625,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13542,11 +12697,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -13619,11 +12769,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13696,11 +12841,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13773,11 +12913,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13850,11 +12985,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13927,11 +13057,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14004,11 +13129,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14081,11 +13201,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -14153,11 +13268,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14230,11 +13340,6 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14302,11 +13407,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14374,11 +13474,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14446,11 +13541,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14523,11 +13613,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14595,11 +13680,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14667,11 +13747,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14739,11 +13814,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14816,11 +13886,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -14893,11 +13958,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -14970,11 +14030,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15047,11 +14102,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15124,11 +14174,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -15201,11 +14246,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15278,11 +14318,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15355,11 +14390,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -15427,11 +14457,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15499,11 +14524,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15576,11 +14596,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15653,11 +14668,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -15725,11 +14735,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15802,11 +14807,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15879,11 +14879,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15956,11 +14951,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16028,11 +15018,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16105,11 +15090,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16177,11 +15157,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16249,11 +15224,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16326,11 +15296,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16398,11 +15363,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16475,11 +15435,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16552,11 +15507,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16860,11 +15810,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17091,11 +16036,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -17168,11 +16108,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -17245,11 +16180,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17317,11 +16247,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17394,11 +16319,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17471,11 +16391,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17548,11 +16463,6 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17625,11 +16535,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17697,11 +16602,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17774,11 +16674,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -17851,11 +16746,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17928,11 +16818,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -18005,11 +16890,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18082,11 +16962,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18159,11 +17034,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18236,11 +17106,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18313,11 +17178,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18390,11 +17250,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -18467,11 +17322,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -18544,11 +17394,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18621,11 +17466,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18698,11 +17538,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18775,11 +17610,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18852,11 +17682,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18929,11 +17754,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19006,11 +17826,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19083,11 +17898,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19160,11 +17970,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19237,11 +18042,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19314,11 +18114,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19391,11 +18186,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19468,11 +18258,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19545,11 +18330,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19622,11 +18402,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -19699,11 +18474,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -19853,11 +18623,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19930,11 +18695,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20084,11 +18844,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20161,11 +18916,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20238,11 +18988,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20310,11 +19055,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20382,11 +19122,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20526,11 +19261,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20598,11 +19328,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20670,11 +19395,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20742,11 +19462,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20814,11 +19529,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20886,11 +19596,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21030,11 +19735,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21102,11 +19802,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21174,11 +19869,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21246,11 +19936,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21318,11 +20003,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -21390,11 +20070,6 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21462,11 +20137,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21534,11 +20204,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21606,11 +20271,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21678,11 +20338,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21750,11 +20405,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21822,11 +20472,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -21894,11 +20539,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21966,11 +20606,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -22038,11 +20673,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22110,11 +20740,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22182,11 +20807,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22254,11 +20874,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -22326,11 +20941,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22398,11 +21008,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22470,11 +21075,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22542,11 +21142,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22609,11 +21204,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22681,11 +21271,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22753,11 +21338,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -22825,11 +21405,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22897,11 +21472,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22969,11 +21539,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23041,11 +21606,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23113,11 +21673,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -23185,11 +21740,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -23257,11 +21807,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23329,11 +21874,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -23396,11 +21936,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23463,11 +21998,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23535,11 +22065,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23607,11 +22132,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23679,11 +22199,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23751,11 +22266,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23823,11 +22333,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23895,11 +22400,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -23967,11 +22467,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -24039,11 +22534,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -24111,11 +22601,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24183,11 +22668,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24255,11 +22735,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24327,11 +22802,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24399,11 +22869,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24466,11 +22931,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24610,11 +23070,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -24682,11 +23137,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24754,11 +23204,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24826,11 +23271,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24898,11 +23338,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25042,11 +23477,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25114,11 +23544,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25258,11 +23683,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -25325,11 +23745,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25397,11 +23812,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25469,11 +23879,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25608,11 +24013,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25680,11 +24080,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25752,11 +24147,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -25824,11 +24214,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25891,11 +24276,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25958,11 +24338,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26030,11 +24405,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26102,11 +24472,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26174,11 +24539,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26246,11 +24606,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26318,11 +24673,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -26390,11 +24740,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26462,11 +24807,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26534,11 +24874,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26606,11 +24941,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26678,11 +25008,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26745,11 +25070,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26812,11 +25132,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26884,11 +25199,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26956,11 +25266,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27023,11 +25328,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27095,11 +25395,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -27162,11 +25457,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27234,11 +25524,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27306,11 +25591,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27378,11 +25658,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27445,11 +25720,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27517,11 +25787,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -27589,11 +25854,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27656,11 +25916,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27728,11 +25983,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27800,11 +26050,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27872,11 +26117,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27944,11 +26184,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -28083,11 +26318,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28155,11 +26385,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28227,11 +26452,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28366,11 +26586,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28510,11 +26725,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -28798,11 +27008,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28870,11 +27075,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28942,11 +27142,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29014,11 +27209,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29086,11 +27276,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29158,11 +27343,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29230,11 +27410,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29302,11 +27477,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -29374,11 +27544,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29446,11 +27611,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29518,11 +27678,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -29590,11 +27745,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29662,11 +27812,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29734,11 +27879,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29806,11 +27946,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29878,11 +28013,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29950,11 +28080,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30022,11 +28147,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30094,11 +28214,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30166,11 +28281,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30238,11 +28348,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30310,11 +28415,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30382,11 +28482,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30454,11 +28549,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30526,11 +28616,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30598,11 +28683,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30670,11 +28750,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30742,11 +28817,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30814,11 +28884,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30886,11 +28951,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30958,11 +29018,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31030,11 +29085,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31102,11 +29152,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31174,11 +29219,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31246,11 +29286,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31318,11 +29353,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31390,11 +29420,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -31462,11 +29487,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -31534,11 +29554,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -31606,11 +29621,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -31678,11 +29688,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31750,11 +29755,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31822,11 +29822,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31889,11 +29884,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -31961,11 +29951,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32033,11 +30018,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32105,11 +30085,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32177,11 +30152,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32249,11 +30219,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32321,11 +30286,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32393,11 +30353,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -32465,11 +30420,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32532,11 +30482,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32599,11 +30544,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32671,11 +30611,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32743,11 +30678,6 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32815,11 +30745,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32887,11 +30812,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -32959,11 +30879,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -33031,11 +30946,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -33103,11 +31013,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33170,11 +31075,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33237,11 +31137,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33309,11 +31204,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33381,11 +31271,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33453,11 +31338,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33525,11 +31405,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33597,11 +31472,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33669,11 +31539,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33741,11 +31606,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33813,11 +31673,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33885,11 +31740,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -33957,11 +31807,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34029,11 +31874,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34101,11 +31941,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34173,11 +32008,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34245,11 +32075,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34317,11 +32142,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34389,11 +32209,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34461,11 +32276,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34533,11 +32343,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34605,11 +32410,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -34677,11 +32477,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -34749,11 +32544,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -34821,11 +32611,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -34893,11 +32678,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -34965,11 +32745,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35037,11 +32812,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35109,11 +32879,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35181,11 +32946,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35253,11 +33013,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35325,11 +33080,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35397,11 +33147,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35469,11 +33214,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35541,11 +33281,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35613,11 +33348,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35685,11 +33415,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35757,11 +33482,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35829,11 +33549,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35901,11 +33616,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -35973,11 +33683,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -36045,11 +33750,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36117,11 +33817,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36189,11 +33884,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36261,11 +33951,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36333,11 +34018,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36405,11 +34085,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36477,11 +34152,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36549,11 +34219,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36621,11 +34286,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36693,11 +34353,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36765,11 +34420,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36837,11 +34487,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36909,11 +34554,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -36981,11 +34621,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37053,11 +34688,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37125,11 +34755,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37197,11 +34822,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37269,11 +34889,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37341,11 +34956,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37413,11 +35023,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37485,11 +35090,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37557,11 +35157,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37629,11 +35224,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -37711,11 +35301,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37865,11 +35450,6 @@
           <t xml:space="preserve">22.09.23</t>
         </is>
       </c>
-      <c r="L505" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M505" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37947,11 +35527,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M506" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38029,11 +35604,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M507" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38111,11 +35681,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M508" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38193,11 +35758,6 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M509" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38275,11 +35835,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M510" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38357,11 +35912,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L511" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M511" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38439,11 +35989,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L512" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M512" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38521,11 +36066,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M513" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38603,11 +36143,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M514" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38685,11 +36220,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M515" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38767,11 +36297,6 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M516" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38814,11 +36339,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M517" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38861,11 +36381,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M518" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38908,11 +36423,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M519" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38955,11 +36465,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M520" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39002,11 +36507,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M521" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39049,11 +36549,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M522" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39096,11 +36591,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M523" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39143,11 +36633,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M524" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39190,11 +36675,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M525" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39237,11 +36717,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M526" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39284,11 +36759,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M527" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39331,11 +36801,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M528" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39378,11 +36843,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M529" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39425,11 +36885,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M530" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39472,11 +36927,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M531" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39519,11 +36969,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M532" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39566,11 +37011,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M533" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39613,11 +37053,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M534" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39660,11 +37095,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M535" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39707,11 +37137,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M536" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39754,11 +37179,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M537" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39801,11 +37221,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M538" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39848,11 +37263,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M539" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39895,11 +37305,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M540" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39942,11 +37347,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M541" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39989,11 +37389,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M542" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40036,11 +37431,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M543" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40083,11 +37473,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M544" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40130,11 +37515,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M545" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40177,11 +37557,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M546" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40224,11 +37599,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L547" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M547" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40271,11 +37641,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M548" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40318,11 +37683,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M549" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40365,11 +37725,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M550" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40412,11 +37767,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L551" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M551" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40459,11 +37809,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M552" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40506,11 +37851,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M553" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40553,11 +37893,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M554" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40600,11 +37935,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M555" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40647,11 +37977,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M556" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40694,11 +38019,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M557" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40741,11 +38061,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M558" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40788,11 +38103,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M559" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40835,11 +38145,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M560" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40882,11 +38187,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M561" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40929,11 +38229,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M562" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40976,11 +38271,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M563" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41023,11 +38313,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M564" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41070,11 +38355,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M565" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41117,11 +38397,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M566" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41164,11 +38439,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M567" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41211,11 +38481,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M568" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41258,11 +38523,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L569" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M569" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41305,11 +38565,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M570" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41352,11 +38607,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M571" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41399,11 +38649,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M572" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41446,11 +38691,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M573" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41493,11 +38733,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M574" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41540,11 +38775,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M575" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41587,11 +38817,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M576" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41634,11 +38859,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M577" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41681,11 +38901,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M578" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41728,11 +38943,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M579" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41775,11 +38985,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M580" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41822,11 +39027,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M581" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41869,11 +39069,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L582" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M582" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41916,11 +39111,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L583" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M583" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41963,11 +39153,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L584" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M584" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42010,11 +39195,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L585" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M585" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42057,11 +39237,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L586" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M586" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42104,11 +39279,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L587" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M587" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42151,11 +39321,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L588" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M588" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42198,11 +39363,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L589" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M589" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42245,11 +39405,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L590" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M590" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42292,11 +39447,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M591" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42339,11 +39489,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L592" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M592" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42386,11 +39531,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L593" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M593" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42433,11 +39573,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L594" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M594" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42480,11 +39615,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L595" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M595" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42527,11 +39657,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L596" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M596" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42574,11 +39699,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L597" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M597" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42621,11 +39741,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L598" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M598" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42668,11 +39783,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L599" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M599" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42715,11 +39825,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L600" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M600" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42762,11 +39867,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M601" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42809,11 +39909,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M602" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42856,11 +39951,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M603" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42903,11 +39993,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M604" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42950,11 +40035,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M605" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -42997,11 +40077,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M606" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43044,11 +40119,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L607" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M607" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43091,11 +40161,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M608" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43138,11 +40203,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M609" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43185,11 +40245,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M610" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43232,11 +40287,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M611" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43279,11 +40329,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L612" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M612" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43326,11 +40371,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L613" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M613" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43373,11 +40413,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M614" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43420,11 +40455,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L615" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M615" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43467,11 +40497,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M616" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43514,11 +40539,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M617" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43561,11 +40581,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L618" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M618" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43608,11 +40623,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M619" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43655,11 +40665,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L620" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M620" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43702,11 +40707,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M621" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43749,11 +40749,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M622" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43796,11 +40791,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M623" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43843,11 +40833,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L624" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M624" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43890,11 +40875,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L625" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M625" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43937,11 +40917,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L626" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M626" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -43984,11 +40959,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L627" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M627" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44031,11 +41001,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L628" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M628" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44078,11 +41043,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L629" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M629" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44125,11 +41085,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L630" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M630" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44172,11 +41127,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L631" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M631" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44219,11 +41169,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M632" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44266,11 +41211,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M633" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44313,11 +41253,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L634" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M634" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44360,11 +41295,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M635" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44407,11 +41337,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M636" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44454,11 +41379,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M637" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44501,11 +41421,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M638" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44548,11 +41463,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M639" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44595,11 +41505,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M640" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44642,11 +41547,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L641" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M641" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44689,11 +41589,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M642" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44736,11 +41631,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M643" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44783,11 +41673,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L644" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M644" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44830,11 +41715,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M645" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44877,11 +41757,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L646" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M646" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44924,11 +41799,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M647" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -44971,11 +41841,6 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
       <c r="M648" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -45016,11 +41881,6 @@
       <c r="J649" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L649" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -199,6 +199,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -276,6 +281,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -353,6 +363,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -430,6 +445,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -507,6 +527,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -584,6 +609,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -661,6 +691,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -738,6 +773,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -815,6 +855,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -892,6 +937,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -969,6 +1019,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1046,6 +1101,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1123,6 +1183,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1200,6 +1265,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1277,6 +1347,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1354,6 +1429,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1431,6 +1511,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1508,6 +1593,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1585,6 +1675,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1662,6 +1757,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1739,6 +1839,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1816,6 +1921,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1893,6 +2003,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -1965,6 +2080,11 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2037,6 +2157,11 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2109,6 +2234,11 @@
           <t xml:space="preserve">27.01.20</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2186,6 +2316,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2263,6 +2398,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2340,6 +2480,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2417,6 +2562,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2494,6 +2644,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2571,6 +2726,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2643,6 +2803,11 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2715,6 +2880,11 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2787,6 +2957,11 @@
           <t xml:space="preserve">04.09.20</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2864,6 +3039,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -2941,6 +3121,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3018,6 +3203,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3095,6 +3285,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3172,6 +3367,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3249,6 +3449,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3326,6 +3531,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3403,6 +3613,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3475,6 +3690,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3547,6 +3767,11 @@
           <t xml:space="preserve">20.07.20</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -3624,6 +3849,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3701,6 +3931,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -3778,6 +4013,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3855,6 +4095,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -3932,6 +4177,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4004,6 +4254,11 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4076,6 +4331,11 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4148,6 +4408,11 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4220,6 +4485,11 @@
           <t xml:space="preserve">08.07.20</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4292,6 +4562,11 @@
           <t xml:space="preserve">31.07.20</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4369,6 +4644,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4446,6 +4726,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -4523,6 +4808,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4600,6 +4890,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -4677,6 +4972,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4754,6 +5054,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4826,6 +5131,11 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4898,6 +5208,11 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -4970,6 +5285,11 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5042,6 +5362,11 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5114,6 +5439,11 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5191,6 +5521,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5268,6 +5603,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5340,6 +5680,11 @@
           <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -5412,6 +5757,11 @@
           <t xml:space="preserve">13.03.20</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -5484,6 +5834,11 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5556,6 +5911,11 @@
           <t xml:space="preserve">14.07.20</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5628,6 +5988,11 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5700,6 +6065,11 @@
           <t xml:space="preserve">10.07.20</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5777,6 +6147,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5854,6 +6229,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -5931,6 +6311,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6008,6 +6393,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6085,6 +6475,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6162,6 +6557,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6239,6 +6639,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6316,6 +6721,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6388,6 +6798,11 @@
           <t xml:space="preserve">28.04.21</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -6465,6 +6880,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6542,6 +6962,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -6619,6 +7044,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -6696,6 +7126,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6773,6 +7208,11 @@
           <t xml:space="preserve">HeLa</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6850,6 +7290,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -6927,6 +7372,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7004,6 +7454,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7081,6 +7536,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7158,6 +7618,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7235,6 +7700,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7312,6 +7782,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7389,6 +7864,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7466,6 +7946,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7543,6 +8028,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7620,6 +8110,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7697,6 +8192,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7774,6 +8274,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7846,6 +8351,11 @@
           <t xml:space="preserve">26.12.19</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -7918,6 +8428,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -7985,6 +8500,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8057,6 +8577,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -8129,6 +8654,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -8201,6 +8731,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -8273,6 +8808,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8345,6 +8885,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8417,6 +8962,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8489,6 +9039,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -8561,6 +9116,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -8633,6 +9193,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8705,6 +9270,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8777,6 +9347,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8849,6 +9424,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8921,6 +9501,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -8993,6 +9578,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9065,6 +9655,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9137,6 +9732,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9209,6 +9809,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9281,6 +9886,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9353,6 +9963,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9425,6 +10040,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9497,6 +10117,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9569,6 +10194,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9641,6 +10271,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9713,6 +10348,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9785,6 +10425,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9857,6 +10502,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -9929,6 +10579,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10001,6 +10656,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10073,6 +10733,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10145,6 +10810,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10217,6 +10887,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10284,6 +10959,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10351,6 +11031,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10423,6 +11108,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10495,6 +11185,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10567,6 +11262,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10639,6 +11339,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10711,6 +11416,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -10783,6 +11493,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -10855,6 +11570,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10927,6 +11647,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -10999,6 +11724,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11071,6 +11801,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11143,6 +11878,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11210,6 +11950,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -11282,6 +12027,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -11349,6 +12099,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11416,6 +12171,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11488,6 +12248,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11560,6 +12325,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11627,6 +12397,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11699,6 +12474,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11766,6 +12546,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11838,6 +12623,11 @@
           <t xml:space="preserve">HepG2</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11905,6 +12695,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -11977,6 +12772,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12049,6 +12849,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12121,6 +12926,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12193,6 +13003,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12265,6 +13080,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12337,6 +13157,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12409,6 +13234,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12481,6 +13311,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12553,6 +13388,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12625,6 +13465,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12697,6 +13542,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -12769,6 +13619,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -12841,6 +13696,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12913,6 +13773,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -12985,6 +13850,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13057,6 +13927,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13129,6 +14004,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13201,6 +14081,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13268,6 +14153,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13340,6 +14230,11 @@
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13407,6 +14302,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13474,6 +14374,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13541,6 +14446,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13613,6 +14523,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13680,6 +14595,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13747,6 +14667,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13814,6 +14739,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -13886,6 +14816,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -13958,6 +14893,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -14030,6 +14970,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14102,6 +15047,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -14174,6 +15124,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -14246,6 +15201,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14318,6 +15278,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14390,6 +15355,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -14457,6 +15427,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14524,6 +15499,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14596,6 +15576,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14668,6 +15653,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -14735,6 +15725,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14807,6 +15802,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14879,6 +15879,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -14951,6 +15956,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -15018,6 +16028,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15090,6 +16105,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -15157,6 +16177,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15224,6 +16249,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15296,6 +16326,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15363,6 +16398,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -15435,6 +16475,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -15507,6 +16552,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -15810,6 +16860,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16036,6 +17091,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16108,6 +17168,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -16180,6 +17245,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16247,6 +17317,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16319,6 +17394,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16391,6 +17471,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16463,6 +17548,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16535,6 +17625,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16602,6 +17697,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16674,6 +17774,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16746,6 +17851,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16818,6 +17928,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -16890,6 +18005,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -16962,6 +18082,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17034,6 +18159,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17106,6 +18236,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17178,6 +18313,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17250,6 +18390,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -17322,6 +18467,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -17394,6 +18544,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17466,6 +18621,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17538,6 +18698,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17610,6 +18775,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17682,6 +18852,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17754,6 +18929,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17826,6 +19006,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17898,6 +19083,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -17970,6 +19160,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18042,6 +19237,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18114,6 +19314,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18186,6 +19391,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18258,6 +19468,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18330,6 +19545,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18402,6 +19622,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -18474,6 +19699,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -18623,6 +19853,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18695,6 +19930,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18844,6 +20084,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18916,6 +20161,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -18988,6 +20238,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19055,6 +20310,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19122,6 +20382,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19261,6 +20526,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -19328,6 +20598,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19395,6 +20670,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19462,6 +20742,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -19529,6 +20814,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19596,6 +20886,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -19735,6 +21030,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -19802,6 +21102,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -19869,6 +21174,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -19936,6 +21246,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20003,6 +21318,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -20070,6 +21390,11 @@
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20137,6 +21462,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20204,6 +21534,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20271,6 +21606,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20338,6 +21678,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20405,6 +21750,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20472,6 +21822,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -20539,6 +21894,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20606,6 +21966,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -20673,6 +22038,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20740,6 +22110,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -20807,6 +22182,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -20874,6 +22254,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -20941,6 +22326,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21008,6 +22398,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21075,6 +22470,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21142,6 +22542,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21204,6 +22609,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21271,6 +22681,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21338,6 +22753,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -21405,6 +22825,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21472,6 +22897,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21539,6 +22969,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21606,6 +23041,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21673,6 +23113,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -21740,6 +23185,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -21807,6 +23257,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -21874,6 +23329,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -21936,6 +23396,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -21998,6 +23463,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22065,6 +23535,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22132,6 +23607,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22199,6 +23679,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22266,6 +23751,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22333,6 +23823,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22400,6 +23895,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -22467,6 +23967,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -22534,6 +24039,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -22601,6 +24111,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22668,6 +24183,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22735,6 +24255,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22802,6 +24327,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22869,6 +24399,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -22931,6 +24466,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23070,6 +24610,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -23137,6 +24682,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23204,6 +24754,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23271,6 +24826,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23338,6 +24898,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23477,6 +25042,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23544,6 +25114,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23683,6 +25258,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -23745,6 +25325,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23812,6 +25397,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -23879,6 +25469,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24013,6 +25608,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24080,6 +25680,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24147,6 +25752,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -24214,6 +25824,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -24276,6 +25891,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24338,6 +25958,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24405,6 +26030,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24472,6 +26102,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -24539,6 +26174,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24606,6 +26246,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24673,6 +26318,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">CisR</t>
@@ -24740,6 +26390,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -24807,6 +26462,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24874,6 +26534,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -24941,6 +26606,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25008,6 +26678,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25070,6 +26745,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25132,6 +26812,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25199,6 +26884,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25266,6 +26956,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25328,6 +27023,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25395,6 +27095,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25457,6 +27162,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25524,6 +27234,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25591,6 +27306,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25658,6 +27378,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25720,6 +27445,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25787,6 +27517,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -25854,6 +27589,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25916,6 +27656,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -25983,6 +27728,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26050,6 +27800,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26117,6 +27872,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26184,6 +27944,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -26318,6 +28083,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26385,6 +28155,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -26452,6 +28227,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26586,6 +28366,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -26725,6 +28510,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -27008,6 +28798,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27075,6 +28870,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27142,6 +28942,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27209,6 +29014,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27276,6 +29086,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27343,6 +29158,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27410,6 +29230,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27477,6 +29302,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -27544,6 +29374,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27611,6 +29446,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27678,6 +29518,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -27745,6 +29590,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27812,6 +29662,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -27879,6 +29734,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -27946,6 +29806,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28013,6 +29878,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28080,6 +29950,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28147,6 +30022,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28214,6 +30094,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -28281,6 +30166,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28348,6 +30238,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28415,6 +30310,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28482,6 +30382,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28549,6 +30454,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28616,6 +30526,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28683,6 +30598,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -28750,6 +30670,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28817,6 +30742,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -28884,6 +30814,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -28951,6 +30886,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29018,6 +30958,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29085,6 +31030,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29152,6 +31102,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29219,6 +31174,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29286,6 +31246,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29353,6 +31318,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29420,6 +31390,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29487,6 +31462,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29554,6 +31534,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29621,6 +31606,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -29688,6 +31678,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29755,6 +31750,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29822,6 +31822,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -29884,6 +31889,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -29951,6 +31961,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30018,6 +32033,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30085,6 +32105,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30152,6 +32177,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30219,6 +32249,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30286,6 +32321,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30353,6 +32393,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30420,6 +32465,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30482,6 +32532,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30544,6 +32599,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30611,6 +32671,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -30678,6 +32743,11 @@
           <t xml:space="preserve">22Rv1</t>
         </is>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30745,6 +32815,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -30812,6 +32887,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30879,6 +32959,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -30946,6 +33031,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -31013,6 +33103,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31075,6 +33170,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31137,6 +33237,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31204,6 +33309,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31271,6 +33381,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31338,6 +33453,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31405,6 +33525,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31472,6 +33597,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31539,6 +33669,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31606,6 +33741,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31673,6 +33813,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31740,6 +33885,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31807,6 +33957,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31874,6 +34029,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -31941,6 +34101,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32008,6 +34173,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32075,6 +34245,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32142,6 +34317,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32209,6 +34389,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32276,6 +34461,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32343,6 +34533,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -32410,6 +34605,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32477,6 +34677,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32544,6 +34749,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32611,6 +34821,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32678,6 +34893,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32745,6 +34965,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32812,6 +35037,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32879,6 +35109,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -32946,6 +35181,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33013,6 +35253,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33080,6 +35325,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33147,6 +35397,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33214,6 +35469,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33281,6 +35541,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33348,6 +35613,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33415,6 +35685,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33482,6 +35757,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33549,6 +35829,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33616,6 +35901,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33683,6 +35973,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
@@ -33750,6 +36045,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -33817,6 +36117,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -33884,6 +36189,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -33951,6 +36261,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34018,6 +36333,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34085,6 +36405,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34152,6 +36477,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34219,6 +36549,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34286,6 +36621,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -34353,6 +36693,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34420,6 +36765,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34487,6 +36837,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34554,6 +36909,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34621,6 +36981,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34688,6 +37053,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34755,6 +37125,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34822,6 +37197,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34889,6 +37269,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -34956,6 +37341,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -35023,6 +37413,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -35090,6 +37485,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -35157,6 +37557,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -35224,6 +37629,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t xml:space="preserve">CabaR</t>
@@ -35301,6 +37711,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35450,6 +37865,11 @@
           <t xml:space="preserve">22.09.23</t>
         </is>
       </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M505" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35527,6 +37947,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M506" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35604,6 +38029,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M507" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35681,6 +38111,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M508" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35758,6 +38193,11 @@
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M509" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35835,6 +38275,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M510" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35912,6 +38357,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M511" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -35989,6 +38439,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M512" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36066,6 +38521,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M513" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36143,6 +38603,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M514" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36220,6 +38685,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M515" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36297,6 +38767,11 @@
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M516" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36339,6 +38814,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M517" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36381,6 +38861,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M518" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36423,6 +38908,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M519" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36465,6 +38955,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M520" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36507,6 +39002,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M521" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36549,6 +39049,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M522" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36591,6 +39096,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M523" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36633,6 +39143,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M524" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36675,6 +39190,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M525" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36717,6 +39237,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M526" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36759,6 +39284,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M527" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36801,6 +39331,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M528" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36843,6 +39378,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M529" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36885,6 +39425,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M530" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36927,6 +39472,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M531" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -36969,6 +39519,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M532" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37011,6 +39566,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M533" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37053,6 +39613,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M534" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37095,6 +39660,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M535" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37137,6 +39707,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M536" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37179,6 +39754,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M537" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37221,6 +39801,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M538" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37263,6 +39848,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M539" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37305,6 +39895,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M540" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37347,6 +39942,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M541" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37389,6 +39989,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M542" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37431,6 +40036,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M543" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37473,6 +40083,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M544" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37515,6 +40130,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M545" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37557,6 +40177,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M546" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37599,6 +40224,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M547" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37641,6 +40271,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M548" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37683,6 +40318,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M549" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37725,6 +40365,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M550" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37767,6 +40412,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M551" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37809,6 +40459,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M552" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37851,6 +40506,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M553" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37893,6 +40553,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M554" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37935,6 +40600,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M555" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -37977,6 +40647,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M556" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38019,6 +40694,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M557" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38061,6 +40741,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M558" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38103,6 +40788,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M559" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38145,6 +40835,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M560" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38187,6 +40882,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M561" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38229,6 +40929,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M562" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38271,6 +40976,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M563" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38313,6 +41023,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M564" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38355,6 +41070,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M565" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38397,6 +41117,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M566" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38439,6 +41164,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M567" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38481,6 +41211,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M568" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38523,6 +41258,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M569" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38565,6 +41305,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M570" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38607,6 +41352,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M571" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38649,6 +41399,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M572" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38691,6 +41446,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M573" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38733,6 +41493,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M574" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38775,6 +41540,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M575" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38817,6 +41587,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M576" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38859,6 +41634,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M577" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38901,6 +41681,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M578" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38943,6 +41728,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M579" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -38985,6 +41775,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M580" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39027,6 +41822,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M581" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39069,6 +41869,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M582" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39111,6 +41916,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M583" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39153,6 +41963,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M584" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39195,6 +42010,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M585" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39237,6 +42057,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M586" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39279,6 +42104,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M587" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39321,6 +42151,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M588" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39363,6 +42198,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M589" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39405,6 +42245,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M590" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39447,6 +42292,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M591" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39489,6 +42339,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M592" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39531,6 +42386,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M593" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39573,6 +42433,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M594" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39615,6 +42480,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M595" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39657,6 +42527,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M596" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39699,6 +42574,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M597" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39741,6 +42621,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M598" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39783,6 +42668,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M599" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39825,6 +42715,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M600" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39867,6 +42762,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M601" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39909,6 +42809,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M602" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39951,6 +42856,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M603" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -39993,6 +42903,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M604" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40035,6 +42950,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M605" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40077,6 +42997,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M606" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40119,6 +43044,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M607" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40161,6 +43091,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M608" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40203,6 +43138,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M609" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40245,6 +43185,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M610" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40287,6 +43232,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M611" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40329,6 +43279,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M612" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40371,6 +43326,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M613" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40413,6 +43373,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M614" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40455,6 +43420,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M615" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40497,6 +43467,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M616" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40539,6 +43514,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M617" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40581,6 +43561,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M618" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40623,6 +43608,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M619" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40665,6 +43655,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M620" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40707,6 +43702,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M621" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40749,6 +43749,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M622" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40791,6 +43796,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M623" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40833,6 +43843,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M624" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40875,6 +43890,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M625" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40917,6 +43937,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M626" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -40959,6 +43984,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M627" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41001,6 +44031,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M628" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41043,6 +44078,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M629" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41085,6 +44125,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M630" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41127,6 +44172,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M631" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41169,6 +44219,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M632" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41211,6 +44266,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M633" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41253,6 +44313,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M634" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41295,6 +44360,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M635" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41337,6 +44407,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M636" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41379,6 +44454,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M637" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41421,6 +44501,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M638" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41463,6 +44548,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M639" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41505,6 +44595,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M640" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41547,6 +44642,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M641" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41589,6 +44689,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M642" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41631,6 +44736,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M643" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41673,6 +44783,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M644" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41715,6 +44830,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M645" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41757,6 +44877,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M646" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41799,6 +44924,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M647" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41841,6 +44971,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
       <c r="M648" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -41881,6 +45016,11 @@
       <c r="J649" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -14155,7 +14155,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -17473,7 +17473,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -21896,7 +21896,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22112,7 +22112,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22256,7 +22256,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -23609,7 +23609,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -24113,7 +24113,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -24401,7 +24401,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -25116,7 +25116,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -25754,7 +25754,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -26248,7 +26248,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -26464,7 +26464,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -27025,7 +27025,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -27447,7 +27447,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -27658,7 +27658,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -28085,7 +28085,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -28944,7 +28944,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -29088,7 +29088,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -29232,7 +29232,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -29592,7 +29592,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -29736,7 +29736,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -29808,7 +29808,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -29952,7 +29952,7 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M400" t="inlineStr">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -30456,7 +30456,7 @@
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -30600,7 +30600,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -30960,7 +30960,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -31248,7 +31248,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -31752,7 +31752,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -31824,7 +31824,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -32107,7 +32107,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -32179,7 +32179,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -32601,7 +32601,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -32817,7 +32817,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -32961,7 +32961,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -33033,7 +33033,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -33105,7 +33105,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -33239,7 +33239,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -33311,7 +33311,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -33383,7 +33383,7 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -33887,7 +33887,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -34031,7 +34031,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -34175,7 +34175,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -34247,7 +34247,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -34391,7 +34391,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34535,7 +34535,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34607,7 +34607,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34751,7 +34751,7 @@
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35183,7 +35183,7 @@
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35399,7 +35399,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35471,7 +35471,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35615,7 +35615,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35687,7 +35687,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35759,7 +35759,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35831,7 +35831,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -35975,7 +35975,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -36047,7 +36047,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -36191,7 +36191,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -36263,7 +36263,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -36335,7 +36335,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -36479,7 +36479,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -36623,7 +36623,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
@@ -36767,7 +36767,7 @@
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
@@ -36911,7 +36911,7 @@
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="L493" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M494" t="inlineStr">
@@ -37127,7 +37127,7 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -37199,7 +37199,7 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
@@ -37487,7 +37487,7 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
@@ -37559,7 +37559,7 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
@@ -37631,7 +37631,7 @@
       </c>
       <c r="L502" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -37713,7 +37713,7 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -38031,7 +38031,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
@@ -38113,7 +38113,7 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M508" t="inlineStr">
@@ -38195,7 +38195,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M509" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
@@ -38359,7 +38359,7 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
@@ -38441,7 +38441,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
@@ -38523,7 +38523,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -38605,7 +38605,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
@@ -38687,7 +38687,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
@@ -38769,7 +38769,7 @@
       </c>
       <c r="L516" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
@@ -38816,7 +38816,7 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
@@ -38863,7 +38863,7 @@
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -38910,7 +38910,7 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
@@ -38957,7 +38957,7 @@
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M520" t="inlineStr">
@@ -39004,7 +39004,7 @@
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
@@ -39051,7 +39051,7 @@
       </c>
       <c r="L522" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M522" t="inlineStr">
@@ -39098,7 +39098,7 @@
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M523" t="inlineStr">
@@ -39145,7 +39145,7 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
@@ -39192,7 +39192,7 @@
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
@@ -39239,7 +39239,7 @@
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M528" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
@@ -39427,7 +39427,7 @@
       </c>
       <c r="L530" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M530" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
@@ -39615,7 +39615,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M535" t="inlineStr">
@@ -39709,7 +39709,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
@@ -39803,7 +39803,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M539" t="inlineStr">
@@ -39897,7 +39897,7 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
@@ -39944,7 +39944,7 @@
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
@@ -39991,7 +39991,7 @@
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
@@ -40038,7 +40038,7 @@
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
@@ -40085,7 +40085,7 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M547" t="inlineStr">
@@ -40273,7 +40273,7 @@
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M548" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
@@ -40367,7 +40367,7 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
@@ -40414,7 +40414,7 @@
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
@@ -40461,7 +40461,7 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
@@ -40555,7 +40555,7 @@
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
@@ -40602,7 +40602,7 @@
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
@@ -40649,7 +40649,7 @@
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
@@ -40696,7 +40696,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
@@ -40743,7 +40743,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
@@ -40790,7 +40790,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
@@ -40837,7 +40837,7 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
@@ -40884,7 +40884,7 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
@@ -40978,7 +40978,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
@@ -41025,7 +41025,7 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
@@ -41072,7 +41072,7 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
@@ -41119,7 +41119,7 @@
       </c>
       <c r="L566" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
@@ -41213,7 +41213,7 @@
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
@@ -41354,7 +41354,7 @@
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M571" t="inlineStr">
@@ -41401,7 +41401,7 @@
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M573" t="inlineStr">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M574" t="inlineStr">
@@ -41542,7 +41542,7 @@
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M575" t="inlineStr">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="L576" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
@@ -41636,7 +41636,7 @@
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M577" t="inlineStr">
@@ -41683,7 +41683,7 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
@@ -41730,7 +41730,7 @@
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M579" t="inlineStr">
@@ -41777,7 +41777,7 @@
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M580" t="inlineStr">
@@ -41824,7 +41824,7 @@
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M581" t="inlineStr">
@@ -41871,7 +41871,7 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M582" t="inlineStr">
@@ -41918,7 +41918,7 @@
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M583" t="inlineStr">
@@ -41965,7 +41965,7 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M584" t="inlineStr">
@@ -42012,7 +42012,7 @@
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M585" t="inlineStr">
@@ -42059,7 +42059,7 @@
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M586" t="inlineStr">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M587" t="inlineStr">
@@ -42153,7 +42153,7 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M588" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M589" t="inlineStr">
@@ -42247,7 +42247,7 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M590" t="inlineStr">
@@ -42294,7 +42294,7 @@
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M591" t="inlineStr">
@@ -42341,7 +42341,7 @@
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M592" t="inlineStr">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
@@ -42435,7 +42435,7 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
@@ -42482,7 +42482,7 @@
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="L596" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M596" t="inlineStr">
@@ -42576,7 +42576,7 @@
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
@@ -42623,7 +42623,7 @@
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="L600" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M600" t="inlineStr">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
@@ -42811,7 +42811,7 @@
       </c>
       <c r="L602" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
@@ -42858,7 +42858,7 @@
       </c>
       <c r="L603" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M603" t="inlineStr">
@@ -42905,7 +42905,7 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
@@ -42999,7 +42999,7 @@
       </c>
       <c r="L606" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M606" t="inlineStr">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="L607" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M607" t="inlineStr">
@@ -43093,7 +43093,7 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
@@ -43234,7 +43234,7 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
@@ -43281,7 +43281,7 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M612" t="inlineStr">
@@ -43328,7 +43328,7 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
@@ -43469,7 +43469,7 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M616" t="inlineStr">
@@ -43516,7 +43516,7 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M620" t="inlineStr">
@@ -43704,7 +43704,7 @@
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M621" t="inlineStr">
@@ -43751,7 +43751,7 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M623" t="inlineStr">
@@ -43845,7 +43845,7 @@
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M625" t="inlineStr">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M626" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M627" t="inlineStr">
@@ -44033,7 +44033,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -44127,7 +44127,7 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M630" t="inlineStr">
@@ -44174,7 +44174,7 @@
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -44221,7 +44221,7 @@
       </c>
       <c r="L632" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M632" t="inlineStr">
@@ -44268,7 +44268,7 @@
       </c>
       <c r="L633" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M633" t="inlineStr">
@@ -44315,7 +44315,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M634" t="inlineStr">
@@ -44362,7 +44362,7 @@
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
@@ -44456,7 +44456,7 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
@@ -44503,7 +44503,7 @@
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M638" t="inlineStr">
@@ -44550,7 +44550,7 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
@@ -44597,7 +44597,7 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
@@ -44644,7 +44644,7 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
@@ -44691,7 +44691,7 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M643" t="inlineStr">
@@ -44785,7 +44785,7 @@
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M644" t="inlineStr">
@@ -44832,7 +44832,7 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
@@ -44879,7 +44879,7 @@
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M646" t="inlineStr">
@@ -44926,7 +44926,7 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M648" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">

--- a/cellstocks/data/baris.xlsx
+++ b/cellstocks/data/baris.xlsx
@@ -206,7 +206,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -288,7 +288,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -452,7 +452,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -18705,7 +18705,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -19013,7 +19013,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -20605,7 +20605,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -20677,7 +20677,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -21037,7 +21037,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -22045,7 +22045,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -22477,7 +22477,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -23470,7 +23470,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -24545,7 +24545,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -25121,7 +25121,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25615,7 +25615,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25898,7 +25898,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25965,7 +25965,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -26181,7 +26181,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -26541,7 +26541,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -26963,7 +26963,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -27241,7 +27241,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -28023,7 +28023,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -28877,7 +28877,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -28949,7 +28949,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -29165,7 +29165,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -29885,7 +29885,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -30245,7 +30245,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -30389,7 +30389,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -30461,7 +30461,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -30821,7 +30821,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -30893,7 +30893,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -31181,7 +31181,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -31685,7 +31685,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -31757,7 +31757,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -32112,7 +32112,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -32606,7 +32606,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -32822,7 +32822,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -33388,7 +33388,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -33460,7 +33460,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -33820,7 +33820,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -34180,7 +34180,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -34324,7 +34324,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -34396,7 +34396,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -34468,7 +34468,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -34540,7 +34540,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -36628,7 +36628,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -37718,7 +37718,7 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
@@ -37795,7 +37795,7 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -37872,7 +37872,7 @@
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N505" t="inlineStr">
@@ -37954,7 +37954,7 @@
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N506" t="inlineStr">
@@ -38036,7 +38036,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -38118,7 +38118,7 @@
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N508" t="inlineStr">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N510" t="inlineStr">
@@ -38364,7 +38364,7 @@
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -38446,7 +38446,7 @@
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N512" t="inlineStr">
@@ -38528,7 +38528,7 @@
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N513" t="inlineStr">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
@@ -38692,7 +38692,7 @@
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N515" t="inlineStr">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -38821,7 +38821,7 @@
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N517" t="inlineStr">
@@ -38868,7 +38868,7 @@
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N518" t="inlineStr">
@@ -38915,7 +38915,7 @@
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
@@ -38962,7 +38962,7 @@
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N520" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
@@ -39056,7 +39056,7 @@
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -39103,7 +39103,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -39150,7 +39150,7 @@
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
@@ -39197,7 +39197,7 @@
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
@@ -39244,7 +39244,7 @@
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
@@ -39291,7 +39291,7 @@
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
@@ -39338,7 +39338,7 @@
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N528" t="inlineStr">
@@ -39385,7 +39385,7 @@
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N529" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N530" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N531" t="inlineStr">
@@ -39526,7 +39526,7 @@
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
@@ -39573,7 +39573,7 @@
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N533" t="inlineStr">
@@ -39620,7 +39620,7 @@
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N534" t="inlineStr">
@@ -39667,7 +39667,7 @@
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N535" t="inlineStr">
@@ -39714,7 +39714,7 @@
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N536" t="inlineStr">
@@ -39761,7 +39761,7 @@
       </c>
       <c r="M537" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N537" t="inlineStr">
@@ -39808,7 +39808,7 @@
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N538" t="inlineStr">
@@ -39855,7 +39855,7 @@
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N539" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N540" t="inlineStr">
@@ -39949,7 +39949,7 @@
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N541" t="inlineStr">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
@@ -40043,7 +40043,7 @@
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N543" t="inlineStr">
@@ -40090,7 +40090,7 @@
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N544" t="inlineStr">
@@ -40137,7 +40137,7 @@
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N545" t="inlineStr">
@@ -40184,7 +40184,7 @@
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
@@ -40231,7 +40231,7 @@
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
@@ -40372,7 +40372,7 @@
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -40419,7 +40419,7 @@
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -40607,7 +40607,7 @@
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -40654,7 +40654,7 @@
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -40795,7 +40795,7 @@
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -40842,7 +40842,7 @@
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
@@ -40889,7 +40889,7 @@
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
@@ -40983,7 +40983,7 @@
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
@@ -41030,7 +41030,7 @@
       </c>
       <c r="M564" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N564" t="inlineStr">
@@ -41077,7 +41077,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -41124,7 +41124,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -41171,7 +41171,7 @@
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
@@ -41218,7 +41218,7 @@
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
@@ -41265,7 +41265,7 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
@@ -41312,7 +41312,7 @@
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -41359,7 +41359,7 @@
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N571" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N572" t="inlineStr">
@@ -41453,7 +41453,7 @@
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N573" t="inlineStr">
@@ -41500,7 +41500,7 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N574" t="inlineStr">
@@ -41547,7 +41547,7 @@
       </c>
       <c r="M575" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N575" t="inlineStr">
@@ -41594,7 +41594,7 @@
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N576" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N577" t="inlineStr">
@@ -41688,7 +41688,7 @@
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N578" t="inlineStr">
@@ -41735,7 +41735,7 @@
       </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N579" t="inlineStr">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N580" t="inlineStr">
@@ -41829,7 +41829,7 @@
       </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N581" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
@@ -41923,7 +41923,7 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N583" t="inlineStr">
@@ -41970,7 +41970,7 @@
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N584" t="inlineStr">
@@ -42017,7 +42017,7 @@
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N585" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N586" t="inlineStr">
@@ -42111,7 +42111,7 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
@@ -42205,7 +42205,7 @@
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
@@ -42252,7 +42252,7 @@
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
@@ -42393,7 +42393,7 @@
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N593" t="inlineStr">
@@ -42440,7 +42440,7 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
@@ -42487,7 +42487,7 @@
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
@@ -42534,7 +42534,7 @@
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N596" t="inlineStr">
@@ -42581,7 +42581,7 @@
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
@@ -42628,7 +42628,7 @@
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
@@ -42675,7 +42675,7 @@
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
@@ -42722,7 +42722,7 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
@@ -42769,7 +42769,7 @@
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
@@ -42863,7 +42863,7 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
@@ -42910,7 +42910,7 @@
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
@@ -42957,7 +42957,7 @@
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
@@ -43004,7 +43004,7 @@
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
@@ -43051,7 +43051,7 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
@@ -43145,7 +43145,7 @@
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
@@ -43239,7 +43239,7 @@
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
@@ -43286,7 +43286,7 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
@@ -43333,7 +43333,7 @@
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N613" t="inlineStr">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N614" t="inlineStr">
@@ -43427,7 +43427,7 @@
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
@@ -43474,7 +43474,7 @@
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N616" t="inlineStr">
@@ -43521,7 +43521,7 @@
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N617" t="inlineStr">
@@ -43568,7 +43568,7 @@
       </c>
       <c r="M618" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N618" t="inlineStr">
@@ -43615,7 +43615,7 @@
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N619" t="inlineStr">
@@ -43662,7 +43662,7 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N620" t="inlineStr">
@@ -43709,7 +43709,7 @@
       </c>
       <c r="M621" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N621" t="inlineStr">
@@ -43756,7 +43756,7 @@
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N622" t="inlineStr">
@@ -43803,7 +43803,7 @@
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N623" t="inlineStr">
@@ -43850,7 +43850,7 @@
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N624" t="inlineStr">
@@ -43897,7 +43897,7 @@
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
@@ -43944,7 +43944,7 @@
       </c>
       <c r="M626" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N626" t="inlineStr">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N627" t="inlineStr">
@@ -44038,7 +44038,7 @@
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N628" t="inlineStr">
@@ -44085,7 +44085,7 @@
       </c>
       <c r="M629" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N629" t="inlineStr">
@@ -44132,7 +44132,7 @@
       </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N630" t="inlineStr">
@@ -44179,7 +44179,7 @@
       </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N631" t="inlineStr">
@@ -44226,7 +44226,7 @@
       </c>
       <c r="M632" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N632" t="inlineStr">
@@ -44273,7 +44273,7 @@
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N633" t="inlineStr">
@@ -44320,7 +44320,7 @@
       </c>
       <c r="M634" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N634" t="inlineStr">
@@ -44367,7 +44367,7 @@
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N635" t="inlineStr">
@@ -44414,7 +44414,7 @@
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N636" t="inlineStr">
@@ -44461,7 +44461,7 @@
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="M638" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N638" t="inlineStr">
@@ -44555,7 +44555,7 @@
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N639" t="inlineStr">
@@ -44602,7 +44602,7 @@
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
@@ -44649,7 +44649,7 @@
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N641" t="inlineStr">
@@ -44696,7 +44696,7 @@
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N642" t="inlineStr">
@@ -44743,7 +44743,7 @@
       </c>
       <c r="M643" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N643" t="inlineStr">
@@ -44790,7 +44790,7 @@
       </c>
       <c r="M644" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N644" t="inlineStr">
@@ -44837,7 +44837,7 @@
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N645" t="inlineStr">
@@ -44884,7 +44884,7 @@
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N646" t="inlineStr">
@@ -44931,7 +44931,7 @@
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N647" t="inlineStr">
@@ -44978,7 +44978,7 @@
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N648" t="inlineStr">
@@ -45025,7 +45025,7 @@
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="N649" t="inlineStr">
